--- a/regressor_scores_r2.xlsx
+++ b/regressor_scores_r2.xlsx
@@ -543,7 +543,7 @@
         <v>0.641</v>
       </c>
       <c r="E5" t="n">
-        <v>0.99</v>
+        <v>0.989</v>
       </c>
       <c r="F5" t="n">
         <v>0.996</v>
